--- a/Projects/Jaden Ivey.xlsx
+++ b/Projects/Jaden Ivey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1D355A-0787-2342-9DEE-239C35F2060A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C86CA8-6B43-844F-BE02-213E19CD937B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="11" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" activeTab="4" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -5216,19 +5216,20 @@
     <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -6512,7 +6513,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70265D1-457E-3245-BC6E-26AC52A9250A}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="5.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -6521,26 +6522,23 @@
     <col min="5" max="5" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
